--- a/outputs/50088.xlsx
+++ b/outputs/50088.xlsx
@@ -116,12 +116,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -317,112 +321,112 @@
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="0" t="s">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="0" t="s">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="0" t="s">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="0" t="s">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" s="0" t="n">
-        <f aca="false">COUNTIF($B$2:$B$11,"A")+COUNTIFS($A$2:$A$11,"A",$B$2:$B$11,"")</f>
+      <c r="E6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <f aca="false">COUNTIF($B:$B,"A")+COUNTIFS($A:$A,"A",$B:$B,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="0" t="n">
-        <f aca="false">COUNTIF($B$2:$B$11,"B")+COUNTIFS($A$2:$A$11,"B",$B$2:$B$11,"")</f>
+      <c r="E7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <f aca="false">COUNTIF($B:$B,"B")+COUNTIFS($A:$A,"B",$B:$B,"")</f>
         <v>5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="A8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="0" t="n">
-        <f aca="false">COUNTIF($B$2:$B$11,"C")+COUNTIFS($A$2:$A$11,"C",$B$2:$B$11,"")</f>
+      <c r="F8" s="1" t="n">
+        <f aca="false">COUNTIF($B:$B,"C")+COUNTIFS($A:$A,"C",$B:$B,"")</f>
         <v>2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="1"/>
+      <c r="A9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
     </row>

--- a/outputs/50088.xlsx
+++ b/outputs/50088.xlsx
@@ -326,7 +326,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -334,7 +334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -342,7 +342,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -350,7 +350,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -358,7 +358,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -369,7 +369,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -380,11 +380,11 @@
         <v>2</v>
       </c>
       <c r="F6" s="1" t="n">
-        <f aca="false">COUNTIF($B:$B,"A")+COUNTIFS($A:$A,"A",$B:$B,"")</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">COUNTIF($B$2:$B$11,"A") + COUNTIFS($A$2:$A$11,"A",$B$2:$B$11,"")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -392,11 +392,11 @@
         <v>3</v>
       </c>
       <c r="F7" s="1" t="n">
-        <f aca="false">COUNTIF($B:$B,"B")+COUNTIFS($A:$A,"B",$B:$B,"")</f>
+        <f aca="false">COUNTIF($B$2:$B$11,"B") + COUNTIFS($A$2:$A$11,"B",$B$2:$B$11,"")</f>
         <v>5</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
@@ -407,11 +407,11 @@
         <v>6</v>
       </c>
       <c r="F8" s="1" t="n">
-        <f aca="false">COUNTIF($B:$B,"C")+COUNTIFS($A:$A,"C",$B:$B,"")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">COUNTIF($B$2:$B$11,"C") + COUNTIFS($A$2:$A$11,"C",$B$2:$B$11,"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
@@ -420,12 +420,12 @@
       </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
